--- a/test_output/workflow_test/scenario_comparison.xlsx
+++ b/test_output/workflow_test/scenario_comparison.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,77 +418,77 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tpa</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>basal_area</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>qmd</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>mean_dbh</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>top_height</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>mean_height</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ccf</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>sdi</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>max_sdi</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>relsdi</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>age</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>volume</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>merchantable_volume</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>board_feet</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>scenario</t>
         </is>
@@ -511,25 +499,25 @@
         <v>600</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8678757465277042</v>
+        <v>0.03272492347489363</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5149789247094966</v>
+        <v>0.09999999999999931</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5042681511465438</v>
+        <v>0.1</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06916539691385787</v>
+        <v>0.6000000000000004</v>
       </c>
       <c r="H2" t="n">
-        <v>5.13538877421817</v>
+        <v>0.3699570011168852</v>
       </c>
       <c r="I2" t="n">
         <v>480</v>
@@ -541,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>112.3458049393424</v>
+        <v>111.9555</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -557,40 +545,40 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="B3" t="n">
-        <v>30.71866907403464</v>
+        <v>0.03222666606191148</v>
       </c>
       <c r="C3" t="n">
-        <v>3.081840487483596</v>
+        <v>0.1004999999999994</v>
       </c>
       <c r="D3" t="n">
-        <v>3.081804573429415</v>
+        <v>0.1005</v>
       </c>
       <c r="E3" t="n">
-        <v>24.18330223700058</v>
+        <v>0.5</v>
       </c>
       <c r="F3" t="n">
-        <v>24.10613305948958</v>
+        <v>0.5</v>
       </c>
       <c r="G3" t="n">
-        <v>2.383401061637665</v>
+        <v>0.002568305610913026</v>
       </c>
       <c r="H3" t="n">
-        <v>89.65922784542758</v>
+        <v>0.3636071337292669</v>
       </c>
       <c r="I3" t="n">
         <v>480</v>
       </c>
       <c r="J3" t="n">
-        <v>1.867900580113075</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>450.0812534530714</v>
+        <v>109.1566858078125</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -606,40 +594,40 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="B4" t="n">
-        <v>71.8903008454833</v>
+        <v>0.03378361035824832</v>
       </c>
       <c r="C4" t="n">
-        <v>4.734594539096623</v>
+        <v>0.1034308403576474</v>
       </c>
       <c r="D4" t="n">
-        <v>4.734099068704251</v>
+        <v>0.1034308403576471</v>
       </c>
       <c r="E4" t="n">
-        <v>38.53131181010473</v>
+        <v>2.930840357647063</v>
       </c>
       <c r="F4" t="n">
-        <v>38.45428315748122</v>
+        <v>2.930840357647063</v>
       </c>
       <c r="G4" t="n">
-        <v>3.818851138070488</v>
+        <v>0.002692386357102526</v>
       </c>
       <c r="H4" t="n">
-        <v>177.0949628351989</v>
+        <v>0.3768702877171708</v>
       </c>
       <c r="I4" t="n">
         <v>480</v>
       </c>
       <c r="J4" t="n">
-        <v>3.689478392399978</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>10</v>
       </c>
       <c r="L4" t="n">
-        <v>1376.955136523368</v>
+        <v>108.0752048434852</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -655,43 +643,43 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="B5" t="n">
-        <v>121.6017994420231</v>
+        <v>3.272277763518062</v>
       </c>
       <c r="C5" t="n">
-        <v>6.226907061890508</v>
+        <v>1.025944713791295</v>
       </c>
       <c r="D5" t="n">
-        <v>6.224037891463015</v>
+        <v>1.025944713791297</v>
       </c>
       <c r="E5" t="n">
-        <v>51.55675097770298</v>
+        <v>8.494005371027981</v>
       </c>
       <c r="F5" t="n">
-        <v>51.47691576655491</v>
+        <v>8.494005371027981</v>
       </c>
       <c r="G5" t="n">
-        <v>5.310947514377122</v>
+        <v>0.2607843245206887</v>
       </c>
       <c r="H5" t="n">
-        <v>268.8283216842783</v>
+        <v>14.74785328270952</v>
       </c>
       <c r="I5" t="n">
         <v>480</v>
       </c>
       <c r="J5" t="n">
-        <v>5.60059003508913</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>15</v>
       </c>
       <c r="L5" t="n">
-        <v>2976.848647266396</v>
+        <v>16.19498646040224</v>
       </c>
       <c r="M5" t="n">
-        <v>877.0260989985096</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -707,40 +695,40 @@
         <v>565</v>
       </c>
       <c r="B6" t="n">
-        <v>168.9319101544706</v>
+        <v>14.50970944161307</v>
       </c>
       <c r="C6" t="n">
-        <v>7.404025875251799</v>
+        <v>2.169908591317202</v>
       </c>
       <c r="D6" t="n">
-        <v>7.395483172797983</v>
+        <v>2.169908591317187</v>
       </c>
       <c r="E6" t="n">
-        <v>61.88301812652696</v>
+        <v>17.18403130010407</v>
       </c>
       <c r="F6" t="n">
-        <v>61.79873719887092</v>
+        <v>17.18403130010407</v>
       </c>
       <c r="G6" t="n">
-        <v>6.631241009593016</v>
+        <v>1.156351950897488</v>
       </c>
       <c r="H6" t="n">
-        <v>348.7742969885265</v>
+        <v>48.64486001131969</v>
       </c>
       <c r="I6" t="n">
         <v>480</v>
       </c>
       <c r="J6" t="n">
-        <v>7.26613118726097</v>
+        <v>1.01343458356916</v>
       </c>
       <c r="K6" t="n">
         <v>20</v>
       </c>
       <c r="L6" t="n">
-        <v>4891.416440311873</v>
+        <v>162.4700410702832</v>
       </c>
       <c r="M6" t="n">
-        <v>1938.046402406422</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -753,46 +741,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B7" t="n">
-        <v>209.7779859194627</v>
+        <v>41.00795529716294</v>
       </c>
       <c r="C7" t="n">
-        <v>8.332232478005091</v>
+        <v>3.690632689947318</v>
       </c>
       <c r="D7" t="n">
-        <v>8.314477293407698</v>
+        <v>3.690632334246227</v>
       </c>
       <c r="E7" t="n">
-        <v>70.28495482032018</v>
+        <v>30.42445637819473</v>
       </c>
       <c r="F7" t="n">
-        <v>70.19377281226988</v>
+        <v>30.42445455129684</v>
       </c>
       <c r="G7" t="n">
-        <v>7.709843018029283</v>
+        <v>2.684043367576244</v>
       </c>
       <c r="H7" t="n">
-        <v>413.3631685703516</v>
+        <v>111.4643276157696</v>
       </c>
       <c r="I7" t="n">
         <v>480</v>
       </c>
       <c r="J7" t="n">
-        <v>8.611732678548993</v>
+        <v>2.3221734919952</v>
       </c>
       <c r="K7" t="n">
         <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>6854.197547012961</v>
+        <v>471.5709069836488</v>
       </c>
       <c r="M7" t="n">
-        <v>3131.503440440872</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>530.4238094679079</v>
+        <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -805,25 +793,25 @@
         <v>400</v>
       </c>
       <c r="B8" t="n">
-        <v>0.5721657080754552</v>
+        <v>0.02181661564992915</v>
       </c>
       <c r="C8" t="n">
-        <v>0.512114676648408</v>
+        <v>0.09999999999999948</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5027385963179115</v>
+        <v>0.1</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04559877201070527</v>
+        <v>0.4000000000000003</v>
       </c>
       <c r="H8" t="n">
-        <v>3.393082218936029</v>
+        <v>0.2466380007445908</v>
       </c>
       <c r="I8" t="n">
         <v>480</v>
@@ -835,7 +823,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>74.8942614420387</v>
+        <v>74.637</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -851,40 +839,40 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B9" t="n">
-        <v>20.32151034321782</v>
+        <v>0.02181497394960159</v>
       </c>
       <c r="C9" t="n">
-        <v>3.082983945489418</v>
+        <v>0.1004999999999996</v>
       </c>
       <c r="D9" t="n">
-        <v>3.082954101582371</v>
+        <v>0.1005</v>
       </c>
       <c r="E9" t="n">
-        <v>24.18674884842458</v>
+        <v>0.5</v>
       </c>
       <c r="F9" t="n">
-        <v>24.11484980770635</v>
+        <v>0.5</v>
       </c>
       <c r="G9" t="n">
-        <v>1.576129479872707</v>
+        <v>0.001738545336618067</v>
       </c>
       <c r="H9" t="n">
-        <v>59.30413071936137</v>
+        <v>0.2461340597551967</v>
       </c>
       <c r="I9" t="n">
         <v>480</v>
       </c>
       <c r="J9" t="n">
-        <v>1.235502723320029</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>297.7702245715509</v>
+        <v>73.89067962374999</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -903,37 +891,37 @@
         <v>384</v>
       </c>
       <c r="B10" t="n">
-        <v>48.04698087037325</v>
+        <v>0.02240571600708528</v>
       </c>
       <c r="C10" t="n">
-        <v>4.789649623770505</v>
+        <v>0.1034308530764516</v>
       </c>
       <c r="D10" t="n">
-        <v>4.789385732980367</v>
+        <v>0.1034308530764517</v>
       </c>
       <c r="E10" t="n">
-        <v>38.59153620314448</v>
+        <v>2.930853076451661</v>
       </c>
       <c r="F10" t="n">
-        <v>38.51915932782047</v>
+        <v>2.930853076451661</v>
       </c>
       <c r="G10" t="n">
-        <v>2.529577127661593</v>
+        <v>0.001785624551635944</v>
       </c>
       <c r="H10" t="n">
-        <v>117.8199230211342</v>
+        <v>0.2499451106144638</v>
       </c>
       <c r="I10" t="n">
         <v>480</v>
       </c>
       <c r="J10" t="n">
-        <v>2.454581729606963</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>10</v>
       </c>
       <c r="L10" t="n">
-        <v>920.0028696739272</v>
+        <v>71.67681993059564</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -949,43 +937,43 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B11" t="n">
-        <v>85.27790412697688</v>
+        <v>2.15858586501564</v>
       </c>
       <c r="C11" t="n">
-        <v>6.457121087095595</v>
+        <v>1.025952011577299</v>
       </c>
       <c r="D11" t="n">
-        <v>6.455638597691814</v>
+        <v>1.025952011577297</v>
       </c>
       <c r="E11" t="n">
-        <v>51.73444978279363</v>
+        <v>8.494060790154208</v>
       </c>
       <c r="F11" t="n">
-        <v>51.66171090147062</v>
+        <v>8.494060790154208</v>
       </c>
       <c r="G11" t="n">
-        <v>3.638795998012128</v>
+        <v>0.1720285982455232</v>
       </c>
       <c r="H11" t="n">
-        <v>185.8419489477265</v>
+        <v>9.728519548198719</v>
       </c>
       <c r="I11" t="n">
         <v>480</v>
       </c>
       <c r="J11" t="n">
-        <v>3.871707269744302</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>15</v>
       </c>
       <c r="L11" t="n">
-        <v>2089.500232641966</v>
+        <v>10.68325569133245</v>
       </c>
       <c r="M11" t="n">
-        <v>659.9120854924157</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -998,43 +986,43 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B12" t="n">
-        <v>122.978023673544</v>
+        <v>9.404851312626747</v>
       </c>
       <c r="C12" t="n">
-        <v>7.859657619844877</v>
+        <v>2.170559671296474</v>
       </c>
       <c r="D12" t="n">
-        <v>7.854838548277741</v>
+        <v>2.170559671296467</v>
       </c>
       <c r="E12" t="n">
-        <v>62.19805114652858</v>
+        <v>17.18898022833458</v>
       </c>
       <c r="F12" t="n">
-        <v>62.12339795175566</v>
+        <v>17.18898022833458</v>
       </c>
       <c r="G12" t="n">
-        <v>4.667939004912062</v>
+        <v>0.7495200511780656</v>
       </c>
       <c r="H12" t="n">
-        <v>247.9794469768551</v>
+        <v>31.52671432166745</v>
       </c>
       <c r="I12" t="n">
         <v>480</v>
       </c>
       <c r="J12" t="n">
-        <v>5.166238478684482</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>20</v>
       </c>
       <c r="L12" t="n">
-        <v>3570.29542632243</v>
+        <v>105.3404303840761</v>
       </c>
       <c r="M12" t="n">
-        <v>1519.75895644745</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1047,46 +1035,46 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B13" t="n">
-        <v>159.8118182681903</v>
+        <v>26.87058630805694</v>
       </c>
       <c r="C13" t="n">
-        <v>9.021723266318652</v>
+        <v>3.694207415652371</v>
       </c>
       <c r="D13" t="n">
-        <v>9.010787872514994</v>
+        <v>3.694207171710148</v>
       </c>
       <c r="E13" t="n">
-        <v>70.60581276820122</v>
+        <v>30.45976081280206</v>
       </c>
       <c r="F13" t="n">
-        <v>70.52696050898382</v>
+        <v>30.45975962818555</v>
       </c>
       <c r="G13" t="n">
-        <v>5.639628513197215</v>
+        <v>1.757198261471533</v>
       </c>
       <c r="H13" t="n">
-        <v>305.1702197634342</v>
+        <v>73.00941179132887</v>
       </c>
       <c r="I13" t="n">
         <v>480</v>
       </c>
       <c r="J13" t="n">
-        <v>6.357712911738212</v>
+        <v>1.521029412319352</v>
       </c>
       <c r="K13" t="n">
         <v>25</v>
       </c>
       <c r="L13" t="n">
-        <v>5234.115318245908</v>
+        <v>309.4337357203097</v>
       </c>
       <c r="M13" t="n">
-        <v>2571.819542471451</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1820.90349058675</v>
+        <v>0</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1099,25 +1087,25 @@
         <v>600</v>
       </c>
       <c r="B14" t="n">
-        <v>0.8411720815708631</v>
+        <v>0.03272492347489363</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5069943332661339</v>
+        <v>0.09999999999999931</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4968057160504162</v>
+        <v>0.1</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05367122386096896</v>
+        <v>0.6000000000000004</v>
       </c>
       <c r="H14" t="n">
-        <v>5.008195045323141</v>
+        <v>0.3699570011168852</v>
       </c>
       <c r="I14" t="n">
         <v>490</v>
@@ -1129,7 +1117,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>112.333564880946</v>
+        <v>111.9555</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1145,40 +1133,40 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="B15" t="n">
-        <v>21.44808834741062</v>
+        <v>0.03250210765218423</v>
       </c>
       <c r="C15" t="n">
-        <v>2.592702385502407</v>
+        <v>0.1004999999999994</v>
       </c>
       <c r="D15" t="n">
-        <v>2.592673664081908</v>
+        <v>0.1005</v>
       </c>
       <c r="E15" t="n">
-        <v>24.18375297992464</v>
+        <v>0.5</v>
       </c>
       <c r="F15" t="n">
-        <v>24.10702014466022</v>
+        <v>0.5</v>
       </c>
       <c r="G15" t="n">
-        <v>1.368501376001441</v>
+        <v>0.002073806221071962</v>
       </c>
       <c r="H15" t="n">
-        <v>67.02377684653456</v>
+        <v>0.3667148870090042</v>
       </c>
       <c r="I15" t="n">
         <v>490</v>
       </c>
       <c r="J15" t="n">
-        <v>1.367832180541522</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>5</v>
       </c>
       <c r="L15" t="n">
-        <v>346.1578730173044</v>
+        <v>110.089648934375</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1194,40 +1182,40 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="B16" t="n">
-        <v>55.69596680848827</v>
+        <v>3.228040900576457</v>
       </c>
       <c r="C16" t="n">
-        <v>4.214191400883609</v>
+        <v>1.01191002977843</v>
       </c>
       <c r="D16" t="n">
-        <v>4.214070745712717</v>
+        <v>1.011910029778428</v>
       </c>
       <c r="E16" t="n">
-        <v>38.85915646213111</v>
+        <v>9.296271123583294</v>
       </c>
       <c r="F16" t="n">
-        <v>38.791585719158</v>
+        <v>9.296271123583294</v>
       </c>
       <c r="G16" t="n">
-        <v>2.705573500517634</v>
+        <v>0.2059660675894747</v>
       </c>
       <c r="H16" t="n">
-        <v>143.6594589645436</v>
+        <v>14.62785304929651</v>
       </c>
       <c r="I16" t="n">
         <v>490</v>
       </c>
       <c r="J16" t="n">
-        <v>2.931825693153951</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>10</v>
       </c>
       <c r="L16" t="n">
-        <v>1097.634637926815</v>
+        <v>17.44920403895267</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -1243,43 +1231,43 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="B17" t="n">
-        <v>97.54561141435521</v>
+        <v>13.34081736942278</v>
       </c>
       <c r="C17" t="n">
-        <v>5.646232302827041</v>
+        <v>2.075168454757626</v>
       </c>
       <c r="D17" t="n">
-        <v>5.645292669087226</v>
+        <v>2.075168454757625</v>
       </c>
       <c r="E17" t="n">
-        <v>53.28495199827061</v>
+        <v>19.25883203071259</v>
       </c>
       <c r="F17" t="n">
-        <v>53.21599421038238</v>
+        <v>19.25883203071259</v>
       </c>
       <c r="G17" t="n">
-        <v>3.910568374110508</v>
+        <v>0.8512146458611096</v>
       </c>
       <c r="H17" t="n">
-        <v>224.1483997736751</v>
+        <v>45.52175254280233</v>
       </c>
       <c r="I17" t="n">
         <v>490</v>
       </c>
       <c r="J17" t="n">
-        <v>4.574457138238267</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>15</v>
       </c>
       <c r="L17" t="n">
-        <v>2484.184793904862</v>
+        <v>75.24681937903392</v>
       </c>
       <c r="M17" t="n">
-        <v>583.8147108601621</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1292,43 +1280,43 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B18" t="n">
-        <v>139.7959448178068</v>
+        <v>33.72706669080414</v>
       </c>
       <c r="C18" t="n">
-        <v>6.814187089268948</v>
+        <v>3.334941309107299</v>
       </c>
       <c r="D18" t="n">
-        <v>6.810958289604335</v>
+        <v>3.334941305326059</v>
       </c>
       <c r="E18" t="n">
-        <v>67.50094061914709</v>
+        <v>31.6857608495868</v>
       </c>
       <c r="F18" t="n">
-        <v>67.42792092452903</v>
+        <v>31.6857608495868</v>
       </c>
       <c r="G18" t="n">
-        <v>5.048660016970894</v>
+        <v>1.965007439562181</v>
       </c>
       <c r="H18" t="n">
-        <v>298.2418834332651</v>
+        <v>95.41822754239998</v>
       </c>
       <c r="I18" t="n">
         <v>490</v>
       </c>
       <c r="J18" t="n">
-        <v>6.08656904965847</v>
+        <v>1.947310766171428</v>
       </c>
       <c r="K18" t="n">
         <v>20</v>
       </c>
       <c r="L18" t="n">
-        <v>4423.967842210355</v>
+        <v>400.3412882729394</v>
       </c>
       <c r="M18" t="n">
-        <v>1567.601450377289</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1341,43 +1329,43 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="B19" t="n">
-        <v>176.9981058109088</v>
+        <v>73.08778275683207</v>
       </c>
       <c r="C19" t="n">
-        <v>7.745009987747919</v>
+        <v>4.954072723286075</v>
       </c>
       <c r="D19" t="n">
-        <v>7.737764072804728</v>
+        <v>4.954071363127405</v>
       </c>
       <c r="E19" t="n">
-        <v>80.35275832372183</v>
+        <v>44.95736669701235</v>
       </c>
       <c r="F19" t="n">
-        <v>80.27318757498355</v>
+        <v>44.95736324173278</v>
       </c>
       <c r="G19" t="n">
-        <v>5.999774663278867</v>
+        <v>3.178063489214111</v>
       </c>
       <c r="H19" t="n">
-        <v>358.9860285040294</v>
+        <v>176.8508936188138</v>
       </c>
       <c r="I19" t="n">
         <v>490</v>
       </c>
       <c r="J19" t="n">
-        <v>7.32624547967407</v>
+        <v>3.609201910588038</v>
       </c>
       <c r="K19" t="n">
         <v>25</v>
       </c>
       <c r="L19" t="n">
-        <v>6614.152094010635</v>
+        <v>1285.764681905672</v>
       </c>
       <c r="M19" t="n">
-        <v>2811.154536816042</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1403,32 +1391,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>scenario</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>final_age</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>final_tpa</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>final_volume</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>final_mean_dbh</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>final_mean_height</t>
         </is>
@@ -1444,16 +1432,16 @@
         <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D2" t="n">
-        <v>6854.197547012961</v>
+        <v>471.5709069836488</v>
       </c>
       <c r="E2" t="n">
-        <v>8.314477293407698</v>
+        <v>3.690632334246227</v>
       </c>
       <c r="F2" t="n">
-        <v>70.19377281226988</v>
+        <v>30.42445455129684</v>
       </c>
     </row>
     <row r="3">
@@ -1466,16 +1454,16 @@
         <v>25</v>
       </c>
       <c r="C3" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D3" t="n">
-        <v>5234.115318245908</v>
+        <v>309.4337357203097</v>
       </c>
       <c r="E3" t="n">
-        <v>9.010787872514994</v>
+        <v>3.694207171710148</v>
       </c>
       <c r="F3" t="n">
-        <v>70.52696050898382</v>
+        <v>30.45975962818555</v>
       </c>
     </row>
     <row r="4">
@@ -1488,16 +1476,16 @@
         <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="D4" t="n">
-        <v>6614.152094010635</v>
+        <v>1285.764681905672</v>
       </c>
       <c r="E4" t="n">
-        <v>7.737764072804728</v>
+        <v>4.954071363127405</v>
       </c>
       <c r="F4" t="n">
-        <v>80.27318757498355</v>
+        <v>44.95736324173278</v>
       </c>
     </row>
   </sheetData>
